--- a/survey_templates/039_molecules_and_compounds_survey--survey_templates.xlsx
+++ b/survey_templates/039_molecules_and_compounds_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C53"/>
+  <dimension ref="A1:C51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -1177,34 +1177,34 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>compound_type_choices</t>
+          <t>molecular_weight_range_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>molecule</t>
+          <t>1-50</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Molecule</t>
+          <t>1-50</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>compound_type_choices</t>
+          <t>molecular_weight_range_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>compound</t>
+          <t>50-100</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Compound</t>
+          <t>50-100</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1-50</t>
+          <t>100-200</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1-50</t>
+          <t>100-200</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>50-100</t>
+          <t>200-500</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>50-100</t>
+          <t>200-500</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>100-200</t>
+          <t>500-1000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>100-200</t>
+          <t>500-1000</t>
         </is>
       </c>
     </row>
@@ -1267,46 +1267,46 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>200-500</t>
+          <t>1000+</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>200-500</t>
+          <t>1000+</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>molecular_weight_range_choices</t>
+          <t>molecular_weight_error_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>500-1000</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>500-1000</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>molecular_weight_range_choices</t>
+          <t>molecular_weight_error_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1000+</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1000+</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1318,46 +1318,46 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>molecular_weight_error_choices</t>
+          <t>molecular_weight_unit_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>dalton</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Dalton</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>molecular_weight_error_choices</t>
+          <t>molecular_weight_unit_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>grams</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Grams</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>dalton</t>
+          <t>grams/moles</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Dalton</t>
+          <t>Grams/Moles</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>grams</t>
+          <t>kilograms</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Grams</t>
+          <t>Kilograms</t>
         </is>
       </c>
     </row>
@@ -1403,46 +1403,46 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>grams/moles</t>
+          <t>milligrams</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Grams/Moles</t>
+          <t>Milligrams</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>molecular_weight_unit_choices</t>
+          <t>molecular_formula_error_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>kilograms</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Kilograms</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>molecular_weight_unit_choices</t>
+          <t>molecular_formula_error_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>milligrams</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Milligrams</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1454,46 +1454,46 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>molecular_formula_error_choices</t>
+          <t>chemical_formula_error_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>molecular_formula_error_choices</t>
+          <t>chemical_formula_error_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1505,46 +1505,46 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>chemical_formula_error_choices</t>
+          <t>chemical_formula_type_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>chemical_formula_error_choices</t>
+          <t>chemical_formula_type_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>inorganic</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Inorganic</t>
         </is>
       </c>
     </row>
@@ -1556,46 +1556,46 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>organic</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Organic</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>chemical_formula_type_choices</t>
+          <t>chemical_formula_type_error_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>inorganic</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Inorganic</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>chemical_formula_type_choices</t>
+          <t>chemical_formula_type_error_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>organic</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Organic</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1607,46 +1607,46 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>chemical_formula_type_error_choices</t>
+          <t>molecular_weight_unit_error_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>chemical_formula_type_error_choices</t>
+          <t>molecular_weight_unit_error_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1658,46 +1658,46 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>molecular_weight_unit_error_choices</t>
+          <t>compound_name_error_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>molecular_weight_unit_error_choices</t>
+          <t>compound_name_error_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1709,46 +1709,46 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>compound_name_error_choices</t>
+          <t>compound_category_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>compound_name_error_choices</t>
+          <t>compound_category_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>inorganic</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Inorganic</t>
         </is>
       </c>
     </row>
@@ -1760,46 +1760,46 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>organic</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Organic</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>compound_category_choices</t>
+          <t>compound_category_error_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>inorganic</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Inorganic</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>compound_category_choices</t>
+          <t>compound_category_error_choices</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>organic</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Organic</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1811,46 +1811,46 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>compound_category_error_choices</t>
+          <t>compound_category_other_error_choices</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>compound_category_error_choices</t>
+          <t>compound_category_other_error_choices</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1862,46 +1862,46 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>compound_category_other_error_choices</t>
+          <t>notes_error_choices</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>compound_category_other_error_choices</t>
+          <t>notes_error_choices</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1913,46 +1913,46 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>notes_error_choices</t>
+          <t>date_of_last_update_error_choices</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>notes_error_choices</t>
+          <t>date_of_last_update_error_choices</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1964,44 +1964,10 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>date_of_last_update_error_choices</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>date_of_last_update_error_choices</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
